--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.431565789814884</v>
+        <v>1.045129440844919</v>
       </c>
       <c r="D2" t="n">
-        <v>8.92185395872761</v>
+        <v>1.449801268293237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F2" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.38797846156803</v>
+        <v>2.013046500004805</v>
       </c>
       <c r="D3" t="n">
-        <v>11.67261752992875</v>
+        <v>1.896800348613422</v>
       </c>
       <c r="E3" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F3" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.42411645407816</v>
+        <v>2.506418923787701</v>
       </c>
       <c r="D4" t="n">
-        <v>14.71393896956216</v>
+        <v>2.391015082553851</v>
       </c>
       <c r="E4" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F4" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.7928030086313</v>
+        <v>4.841330488902586</v>
       </c>
       <c r="D5" t="n">
-        <v>29.0816941077196</v>
+        <v>4.725775292504435</v>
       </c>
       <c r="E5" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F5" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.74177456659429</v>
+        <v>6.133038367071573</v>
       </c>
       <c r="D6" t="n">
-        <v>37.42696514967979</v>
+        <v>6.081881836822967</v>
       </c>
       <c r="E6" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F6" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.99969576234736</v>
+        <v>5.199950561381446</v>
       </c>
       <c r="D7" t="n">
-        <v>31.46823795511913</v>
+        <v>5.113588667706858</v>
       </c>
       <c r="E7" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F7" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.21987647320459</v>
+        <v>7.348229926895746</v>
       </c>
       <c r="D8" t="n">
-        <v>44.52393398900612</v>
+        <v>7.235139273213496</v>
       </c>
       <c r="E8" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F8" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.60613924567987</v>
+        <v>4.648497627422978</v>
       </c>
       <c r="D9" t="n">
-        <v>28.45621934930203</v>
+        <v>4.62413564426158</v>
       </c>
       <c r="E9" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.71630004514892</v>
+        <v>7.7538987573367</v>
       </c>
       <c r="D10" t="n">
-        <v>48.72190045304621</v>
+        <v>7.91730882362001</v>
       </c>
       <c r="E10" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F10" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.02385667601183</v>
+        <v>4.878876709851922</v>
       </c>
       <c r="D11" t="n">
-        <v>30.27636933809098</v>
+        <v>4.919910017439785</v>
       </c>
       <c r="E11" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F11" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.52521152881762</v>
+        <v>6.260346873432864</v>
       </c>
       <c r="D12" t="n">
-        <v>38.79372912393731</v>
+        <v>6.303980982639813</v>
       </c>
       <c r="E12" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F12" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.28574480336233</v>
+        <v>6.871433530546378</v>
       </c>
       <c r="D13" t="n">
-        <v>42.49722401628161</v>
+        <v>6.905798902645762</v>
       </c>
       <c r="E13" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F13" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>49.5523235428855</v>
+        <v>8.052252575718894</v>
       </c>
       <c r="D14" t="n">
-        <v>49.82426904923785</v>
+        <v>8.096443720501151</v>
       </c>
       <c r="E14" t="n">
-        <v>13.14012904548173</v>
+        <v>2.13527096989078</v>
       </c>
       <c r="F14" t="n">
-        <v>13.03516719356871</v>
+        <v>2.118214668954916</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
